--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Biblioteche.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Biblioteche.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="174">
   <si>
     <r>
       <t xml:space="preserve">
@@ -659,7 +659,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
+      <t xml:space="preserve">.
 </t>
     </r>
     <r>
@@ -757,7 +757,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> è scaduta. 
+      <t xml:space="preserve"> è scaduta.
 Per continuare ad usufruire dei servizi bibliotecari, rinnova la tua iscrizione.
 Per ulteriori informazioni su come rinnovare l’iscrizione, [visita questo sito](URL).</t>
     </r>
@@ -1206,7 +1206,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
+      <t xml:space="preserve">.
 Il </t>
     </r>
     <r>
@@ -1224,7 +1224,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">, risulta attualmente in prestito ad altro utente. 
+      <t xml:space="preserve">, risulta attualmente in prestito ad altro utente.
 Riceverai un messaggio in app non appena il </t>
     </r>
     <r>
@@ -1280,7 +1280,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi premium con allegato]</t>
+      <t>[Solo per messaggi con allegato]</t>
     </r>
     <r>
       <rPr>
@@ -1288,8 +1288,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> Trovi la ricevuta del tuo prestito in allegato.
-Per visualizzare la tua ricevuta, [visita questo sito](URL).</t>
+      <t xml:space="preserve"> Trovi la ricevuta del tuo prestito in allegato.</t>
     </r>
   </si>
   <si>
@@ -1316,7 +1315,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> sta per terminare. 
+      <t xml:space="preserve"> sta per terminare.
 Potrai restituire il prestito entro il </t>
     </r>
     <r>
@@ -1467,7 +1466,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> non è possibile. 
+      <t xml:space="preserve"> non è possibile.
 Per procedere con una nuova prenotazione </t>
     </r>
     <r>
@@ -1529,7 +1528,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
+      <t xml:space="preserve">.
 Deve essere restituito il prima possibile.
 </t>
     </r>
@@ -2081,6 +2080,9 @@
     <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
+    <t>Vai alla ricevuta</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -2098,7 +2100,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -2156,7 +2158,7 @@
     <t>Tutti i cittadini che hanno ricevuto una richiesta di sostituzione copia presso una biblioteca comunale per danneggiamento o smarrimento.</t>
   </si>
   <si>
-    <t>Tutti i cittadini che hanno richiesto una consegna  &lt;Libro/Rivista/Dvd/ecc&gt; presso una biblioteca comunale.</t>
+    <t>Tutti i cittadini che hanno richiesto una consegna &lt;Libro/Rivista/Dvd/ecc&gt; presso una biblioteca comunale.</t>
   </si>
   <si>
     <t>Tutti i cittadini che hanno richiesto una consegna documenti presso una biblioteca comunale.</t>
@@ -2249,25 +2251,8 @@
     </r>
   </si>
   <si>
-    <t>✨ Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mancato pagamento
 Il seguente messaggio serve a sollecitare il cittadino per il mancato pagamento ma non costituisce in alcun modo un avviso a valore legale (i.e. notifica).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✨ Allegati Premium — Tramite questa funzionalità Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, puoi allegare documenti all'interno del messaggio.
-Questo messaggio è da utilizzare sia per messaggi Premium, sia per messaggi standard. In caso di messaggio standard, ricorda di eliminare ogni riferimento agli allegati dal corpo del messaggio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di promemoria come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
   </si>
 </sst>
 </file>
@@ -3301,7 +3286,7 @@
         <v>129</v>
       </c>
       <c r="L6" s="34" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M6" s="34" t="s">
         <v>129</v>
@@ -3354,7 +3339,7 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>74</v>
@@ -3440,7 +3425,7 @@
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>129</v>
@@ -3473,7 +3458,7 @@
         <v>129</v>
       </c>
       <c r="L8" s="34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M8" s="34" t="s">
         <v>129</v>
@@ -3526,179 +3511,179 @@
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E9" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="I9" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="J9" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="K9" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="L9" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="M9" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="N9" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="O9" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="P9" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q9" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="R9" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="S9" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="T9" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="U9" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="V9" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="W9" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="X9" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y9" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="Z9" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="AA9" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB9" s="34" t="s">
         <v>138</v>
-      </c>
-      <c r="F9" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="G9" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="I9" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="J9" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="K9" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="L9" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="M9" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="N9" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="O9" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="P9" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q9" s="34" t="s">
-        <v>144</v>
-      </c>
-      <c r="R9" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="S9" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="T9" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="U9" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="V9" s="34" t="s">
-        <v>147</v>
-      </c>
-      <c r="W9" s="34" t="s">
-        <v>147</v>
-      </c>
-      <c r="X9" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y9" s="34" t="s">
-        <v>149</v>
-      </c>
-      <c r="Z9" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="AA9" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="AB9" s="34" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E10" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="I10" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="F10" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="G10" s="34" t="s">
+      <c r="J10" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="K10" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="L10" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="M10" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="N10" s="34" t="s">
+        <v>163</v>
+      </c>
+      <c r="O10" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="P10" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q10" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="R10" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="H10" s="34" t="s">
+      <c r="S10" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="I10" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="J10" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="K10" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="L10" s="34" t="s">
-        <v>160</v>
-      </c>
-      <c r="M10" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="N10" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="O10" s="34" t="s">
-        <v>163</v>
-      </c>
-      <c r="P10" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q10" s="34" t="s">
-        <v>165</v>
-      </c>
-      <c r="R10" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="S10" s="34" t="s">
+      <c r="T10" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="U10" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="V10" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="T10" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="U10" s="34" t="s">
+      <c r="W10" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="X10" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="V10" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="W10" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="X10" s="34" t="s">
-        <v>166</v>
-      </c>
       <c r="Y10" s="34" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Z10" s="34" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AA10" s="34" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AB10" s="34" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>74</v>
@@ -3707,34 +3692,34 @@
         <v>74</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="E11" s="34" t="s">
         <v>74</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="G11" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="H11" s="34" t="s">
-        <v>174</v>
-      </c>
       <c r="I11" s="34" t="s">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="J11" s="34" t="s">
         <v>74</v>
       </c>
       <c r="K11" s="34" t="s">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="L11" s="34" t="s">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="M11" s="34" t="s">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="N11" s="34" t="s">
         <v>74</v>
@@ -3749,25 +3734,25 @@
         <v>74</v>
       </c>
       <c r="R11" s="34" t="s">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="S11" s="34" t="s">
-        <v>176</v>
+        <v>74</v>
       </c>
       <c r="T11" s="34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="U11" s="34" t="s">
         <v>74</v>
       </c>
       <c r="V11" s="34" t="s">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="W11" s="34" t="s">
-        <v>176</v>
+        <v>74</v>
       </c>
       <c r="X11" s="34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Y11" s="34" t="s">
         <v>74</v>
@@ -3779,7 +3764,7 @@
         <v>74</v>
       </c>
       <c r="AB11" s="34" t="s">
-        <v>172</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
